--- a/data/trans_orig/IQ09_D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en días que llevan sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en días que llevan sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 15,08</t>
+          <t>1,57; 14,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 10,15</t>
+          <t>0,0; 10,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,29</t>
+          <t>0,0; 0,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,29</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,95</t>
+          <t>1,57; 7,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,82</t>
+          <t>0,81; 4,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,77</t>
+          <t>0,47; 5,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,64</t>
+          <t>0,88; 5,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,49</t>
+          <t>1,25; 6,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,67</t>
+          <t>0,35; 3,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,17</t>
+          <t>0,58; 4,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,08</t>
+          <t>0,47; 6,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,9</t>
+          <t>1,9; 5,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,95</t>
+          <t>0,84; 3,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,57</t>
+          <t>0,88; 3,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,86</t>
+          <t>1,01; 4,66</t>
         </is>
       </c>
     </row>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 16,27</t>
+          <t>3,13; 17,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,22</t>
+          <t>0,49; 4,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 13,17</t>
+          <t>1,42; 12,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,97</t>
+          <t>0,13; 2,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,95</t>
+          <t>0,83; 9,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 10,08</t>
+          <t>0,89; 10,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,78</t>
+          <t>0,49; 2,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,22</t>
+          <t>1,65; 7,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,63</t>
+          <t>1,2; 4,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,96</t>
+          <t>0,53; 3,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,34</t>
+          <t>0,6; 3,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,66</t>
+          <t>1,66; 5,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,36</t>
+          <t>0,23; 2,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,95</t>
+          <t>0,42; 3,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,18</t>
+          <t>1,05; 5,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,21</t>
+          <t>1,97; 5,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,98</t>
+          <t>0,91; 2,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,76</t>
+          <t>0,71; 2,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,9</t>
+          <t>1,18; 4,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D-Estudios-trans_orig.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 14,06</t>
+          <t>1,47; 14,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,17</t>
+          <t>0,0; 12,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,24</t>
+          <t>0,0; 0,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,52</t>
+          <t>0,0; 9,17</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,7</t>
+          <t>1,46; 8,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,57</t>
+          <t>0,9; 4,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,01</t>
+          <t>0,54; 5,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,94</t>
+          <t>0,97; 5,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,02</t>
+          <t>1,13; 6,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,42</t>
+          <t>0,36; 3,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,31</t>
+          <t>0,72; 4,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,93</t>
+          <t>0,44; 7,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,66</t>
+          <t>1,69; 5,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,08</t>
+          <t>0,78; 3,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,48</t>
+          <t>0,97; 3,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,66</t>
+          <t>0,97; 4,66</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,42</t>
+          <t>0,52; 4,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,57</t>
+          <t>1,43; 12,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,07</t>
+          <t>0,14; 1,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 9,08</t>
+          <t>0,91; 9,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,12</t>
+          <t>0,89; 10,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,64</t>
+          <t>0,44; 2,57</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,4</t>
+          <t>1,52; 7,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,67</t>
+          <t>1,15; 4,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,89</t>
+          <t>0,55; 3,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,41</t>
+          <t>0,53; 3,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,65</t>
+          <t>1,52; 5,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,51</t>
+          <t>0,3; 2,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,13</t>
+          <t>0,45; 3,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,35</t>
+          <t>1,18; 5,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,13</t>
+          <t>2,02; 5,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,87</t>
+          <t>0,89; 2,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,67</t>
+          <t>0,69; 2,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,17</t>
+          <t>1,13; 3,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D-Estudios-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,62 +648,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2,78</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6,88</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2,78</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>5,01</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,41</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1,33; 15,28</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 20,0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,64</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,55</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,41</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0,37; 10,15</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,29</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 14,6</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,25</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,23</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,17</t>
+          <t>1,14; 12,45</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,36</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,81</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,94</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,02</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>2,17</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,26</t>
+          <t>1,1; 6,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,59</t>
+          <t>0,44; 3,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,52</t>
+          <t>0,67; 4,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,45</t>
+          <t>0,42; 6,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,35</t>
+          <t>1,49; 7,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,53</t>
+          <t>0,75; 4,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,22</t>
+          <t>0,5; 4,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 7,32</t>
+          <t>0,89; 5,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,42</t>
+          <t>1,9; 5,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,25</t>
+          <t>0,79; 2,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,64</t>
+          <t>0,9; 3,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,66</t>
+          <t>1,06; 5,06</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,78</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,68</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,08</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,23</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,24</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1,41; 13,17</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3,13; 17,29</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,83</t>
+          <t>0,18; 2,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,18; 16,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,94</t>
+          <t>0,34; 3,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,2</t>
+          <t>1,11; 9,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,38</t>
+          <t>0,93; 10,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,57</t>
+          <t>0,43; 2,62</t>
         </is>
       </c>
     </row>
@@ -1068,54 +1068,54 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,91</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,59</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,68</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,58</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,64</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2,06</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3,41</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
           <t>1,43</t>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>2,37</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,05</t>
+          <t>1,6; 5,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,83</t>
+          <t>0,24; 2,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,97</t>
+          <t>0,41; 2,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,55</t>
+          <t>0,96; 5,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,45</t>
+          <t>1,38; 7,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,38</t>
+          <t>1,15; 4,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,0</t>
+          <t>0,54; 3,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,35</t>
+          <t>0,93; 4,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,4</t>
+          <t>1,97; 5,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,94</t>
+          <t>0,94; 2,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,65</t>
+          <t>0,73; 2,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,96</t>
+          <t>1,37; 4,45</t>
         </is>
       </c>
     </row>
